--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2881-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2881-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3532C02-A12F-4756-A235-44883FE97DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5EE33FF-C389-466C-B5A0-2D77F32961CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{6024319E-E497-474D-897B-16810E7A129F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{7EC6CA4E-A72D-4465-A68D-461B4477D26B}"/>
   </bookViews>
   <sheets>
     <sheet name="2881-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1565,29 +1565,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8522631-9BC3-4C8C-8BF2-832E55C1898A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5BB42AB-533C-4B06-8930-1C722496C10D}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1621,7 +1620,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1657,7 +1656,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1709,7 +1708,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1777,7 +1776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1849,7 +1848,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="13" t="s">
@@ -1877,7 +1876,7 @@
       <c r="W6" s="46"/>
       <c r="X6" s="42"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>2023</v>
       </c>
@@ -1949,7 +1948,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="49"/>
       <c r="B8" s="50"/>
       <c r="C8" s="16" t="s">
@@ -1977,7 +1976,7 @@
       <c r="W8" s="56"/>
       <c r="X8" s="52"/>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -2049,7 +2048,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39"/>
       <c r="B10" s="40"/>
       <c r="C10" s="13" t="s">
@@ -2077,7 +2076,7 @@
       <c r="W10" s="46"/>
       <c r="X10" s="42"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>2021</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="49"/>
       <c r="B12" s="50"/>
       <c r="C12" s="16" t="s">
@@ -2177,7 +2176,7 @@
       <c r="W12" s="56"/>
       <c r="X12" s="52"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2020</v>
       </c>
@@ -2249,7 +2248,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39"/>
       <c r="B14" s="40"/>
       <c r="C14" s="13" t="s">
@@ -2277,7 +2276,7 @@
       <c r="W14" s="46"/>
       <c r="X14" s="42"/>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="57">
         <v>2019</v>
       </c>
@@ -2349,7 +2348,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="59">
         <v>2018</v>
       </c>
@@ -2421,7 +2420,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="57">
         <v>2017</v>
       </c>
@@ -2493,7 +2492,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="59">
         <v>2016</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="57">
         <v>2015</v>
       </c>
@@ -2637,7 +2636,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="59">
         <v>2014</v>
       </c>
@@ -2709,7 +2708,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="57">
         <v>2013</v>
       </c>
@@ -2781,7 +2780,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="59">
         <v>2012</v>
       </c>
@@ -2853,7 +2852,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="57">
         <v>2011</v>
       </c>
@@ -2925,7 +2924,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="59">
         <v>2010</v>
       </c>
@@ -2997,7 +2996,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="57">
         <v>2009</v>
       </c>
@@ -3069,7 +3068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="59">
         <v>2008</v>
       </c>
@@ -3141,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="57">
         <v>2007</v>
       </c>
@@ -3213,7 +3212,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="59">
         <v>2006</v>
       </c>
@@ -3285,7 +3284,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="57">
         <v>2005</v>
       </c>
@@ -3357,7 +3356,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="59">
         <v>2004</v>
       </c>
@@ -3429,7 +3428,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="57">
         <v>2003</v>
       </c>
@@ -3501,7 +3500,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="59">
         <v>2002</v>
       </c>
@@ -3573,7 +3572,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="57">
         <v>2001</v>
       </c>
@@ -3645,7 +3644,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="59" t="s">
         <v>57</v>
       </c>
